--- a/CustomController/schematic/hexController_BOM.xlsx
+++ b/CustomController/schematic/hexController_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Hexapod\CustomController\schematic\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Raven\Documents\Hexapod\CustomController\schematic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64D6C93C-8279-4C05-8052-8D32E07543D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11726982-15A9-4F25-BFEF-651F6F03B044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Item</t>
   </si>
@@ -69,9 +69,6 @@
     <t>Bat Protection Mosfet</t>
   </si>
   <si>
-    <t>IP5306</t>
-  </si>
-  <si>
     <t>1.5uH inductor</t>
   </si>
   <si>
@@ -88,6 +85,21 @@
   </si>
   <si>
     <t>GRM188R60J226MEAOL</t>
+  </si>
+  <si>
+    <t>BQ25628E</t>
+  </si>
+  <si>
+    <t>Rocker switch receptacle</t>
+  </si>
+  <si>
+    <t>Mouser No: 534-3577</t>
+  </si>
+  <si>
+    <t>keystone 3577</t>
+  </si>
+  <si>
+    <t>Keystone</t>
   </si>
 </sst>
 </file>
@@ -149,12 +161,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -437,17 +452,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.5703125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" customWidth="1"/>
-    <col min="4" max="4" width="25.28515625" customWidth="1"/>
-    <col min="5" max="5" width="122.140625" customWidth="1"/>
+    <col min="1" max="1" width="22.5546875" customWidth="1"/>
+    <col min="2" max="2" width="27.88671875" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" customWidth="1"/>
+    <col min="4" max="4" width="25.33203125" customWidth="1"/>
+    <col min="5" max="5" width="122.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -464,7 +479,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -481,7 +496,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -492,7 +507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -503,7 +518,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
@@ -511,40 +526,57 @@
         <v>11</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
         <v>15</v>
       </c>
-      <c r="D6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3</v>
       </c>
       <c r="B8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="s">
-        <v>20</v>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -554,6 +586,7 @@
     <hyperlink ref="D3" r:id="rId3" xr:uid="{B02D7833-63FD-4A9E-A347-16FC26D2C418}"/>
     <hyperlink ref="D4" r:id="rId4" xr:uid="{7A5CD807-B0EC-483E-97BA-A9490CFB581D}"/>
     <hyperlink ref="D5" r:id="rId5" xr:uid="{763C5AE0-342E-491D-89D7-ED38BCFC3DC2}"/>
+    <hyperlink ref="E9" r:id="rId6" xr:uid="{10FE7692-D9EE-42CA-ACCC-DEE9EB4EE68B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
